--- a/Generators/Experiment with utility data leak/diffusion_dataleak/8. Mushroom dataset/TRTR_TSTR_results.xlsx
+++ b/Generators/Experiment with utility data leak/diffusion_dataleak/8. Mushroom dataset/TRTR_TSTR_results.xlsx
@@ -1,21 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TabDDPM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ForestDiffusion" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -510,16 +506,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.999983352755119</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.329448976194804e-05</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999849996249907</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.000075001873271e-05</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -528,10 +524,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999700014999249</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.999700014998055e-05</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -550,7 +546,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.0000 ± 0.0001</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
     </row>
@@ -561,149 +557,149 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998917929082738</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="C3" t="n">
-        <v>3.814362988976479e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999025054365672</v>
+        <v>0.9997835835016291</v>
       </c>
       <c r="E3" t="n">
-        <v>3.436305920243479e-05</v>
+        <v>7.019277779769547e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999100179950515</v>
+        <v>0.9997836064286336</v>
       </c>
       <c r="G3" t="n">
-        <v>9.947206977344203e-05</v>
+        <v>7.017761737132102e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998950052497374</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="I3" t="n">
-        <v>6.873519866439068e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998002330614282</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001498252039287662</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9998200033725814</v>
+        <v>0.9992841547250242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001350057549300141</v>
+        <v>0.0001627286981727347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.999835012740364</v>
+        <v>0.9992842278905526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001414792911934868</v>
+        <v>0.000162754435493228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9998050097495124</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001781062259942747</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0002</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9993757283169635</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001870501502766885</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9994375376797811</v>
+        <v>0.9990677568858726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001685162263673175</v>
+        <v>0.0001608208752413142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9994300667201221</v>
+        <v>0.9990678043284467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002203628791389911</v>
+        <v>0.0001608257005270377</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9994450277486123</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001649917504124697</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
     </row>
@@ -714,47 +710,47 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9430830697519561</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003054622010995107</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9486269064274188</v>
+        <v>0.9425705685761205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002733229331666377</v>
+        <v>0.00466313192865296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9503557108620792</v>
+        <v>0.9427724657852593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004797011192999022</v>
+        <v>0.004363449095413103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9469326533673316</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004340358980694475</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9431 ± 0.0031</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9486 ± 0.0027</t>
+          <t>0.9426 ± 0.0047</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9504 ± 0.0048</t>
+          <t>0.9428 ± 0.0044</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9469 ± 0.0043</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
     </row>
@@ -765,149 +761,149 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8177376394206759</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009463270545125387</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8351441635674031</v>
+        <v>0.8247088934359363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009911515687219402</v>
+        <v>0.003892267554784565</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8380774142407716</v>
+        <v>0.8247249436711384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007023800154772467</v>
+        <v>0.003908421972607685</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8324883755812209</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01907263019534354</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0095</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8351 ± 0.0099</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8381 ± 0.0070</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8325 ± 0.0191</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6532711836191111</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003432765231763527</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7102051701755642</v>
+        <v>0.6593911279336568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002525563014958159</v>
+        <v>0.006146935199587473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6622882541511838</v>
+        <v>0.6671002535150103</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003196371629185143</v>
+        <v>0.005616591844606063</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7656067196640167</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002835651757146686</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.6533 ± 0.0034</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7102 ± 0.0025</t>
+          <t>0.6594 ± 0.0061</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.6623 ± 0.0032</t>
+          <t>0.6671 ± 0.0056</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.7656 ± 0.0028</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6530214749458965</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009110561236368791</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6586554205410092</v>
+        <v>0.6487666462408367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01000642657450882</v>
+        <v>0.0007010223627725054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7262195138345482</v>
+        <v>0.653007104192831</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02162521657245883</v>
+        <v>0.0006802190230959388</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6036898155092245</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02328275950044984</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.6530 ± 0.0091</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.6587 ± 0.0100</t>
+          <t>0.6488 ± 0.0007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.7262 ± 0.0216</t>
+          <t>0.6530 ± 0.0007</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.6037 ± 0.0233</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
     </row>
@@ -918,47 +914,47 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.652688530048277</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003540466283100108</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7111657290688942</v>
+        <v>0.6472491388140823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002515858645437491</v>
+        <v>0.0008797666050638595</v>
       </c>
       <c r="F10" t="n">
-        <v>0.660338278612806</v>
+        <v>0.6522410581225434</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003326244875037613</v>
+        <v>0.0008659629294319769</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7704814759262038</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002684656261806534</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.6527 ± 0.0035</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.7112 ± 0.0025</t>
+          <t>0.6472 ± 0.0009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0033</t>
+          <t>0.6522 ± 0.0009</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.7705 ± 0.0027</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
     </row>
@@ -969,47 +965,47 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6093557516231064</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002206246746399765</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5471586204572338</v>
+        <v>0.5949230921311406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003948342675541275</v>
+        <v>0.001724225896607475</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7669376693867336</v>
+        <v>0.6638581767391858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002744162729666706</v>
+        <v>0.002274716056977206</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4253037348132593</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004574279456311722</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.6094 ± 0.0022</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.5472 ± 0.0039</t>
+          <t>0.5949 ± 0.0017</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7669 ± 0.0027</t>
+          <t>0.6639 ± 0.0023</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.4253 ± 0.0046</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
     </row>
@@ -1186,16 +1182,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.999983352755119</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.329448976194804e-05</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999849996249907</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.000075001873271e-05</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -1204,10 +1200,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999700014999249</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.999700014998055e-05</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1226,68 +1222,68 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.0000 ± 0.0001</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9139836857000165</v>
+        <v>0.4739886798734809</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005142112712232631</v>
+        <v>0.0111696720982644</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9233865186622043</v>
+        <v>0.4632992745037796</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00481176833110665</v>
+        <v>0.007614526669208086</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9127879296386381</v>
+        <v>0.4955554058584816</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004335323832998748</v>
+        <v>0.01923946767949742</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9342882855857206</v>
+        <v>0.4739886798734809</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008863643065170833</v>
+        <v>0.0111696720982644</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.9140 ± 0.0051</t>
+          <t>0.4740 ± 0.0112</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.9234 ± 0.0048</t>
+          <t>0.4633 ± 0.0076</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.9128 ± 0.0043</t>
+          <t>0.4956 ± 0.0192</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.9343 ± 0.0089</t>
+          <t>0.4740 ± 0.0112</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.08599966705510242</v>
+        <v>0.5260113201265191</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.07659848096278632</v>
+        <v>0.5367007254962204</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08721207036136192</v>
+        <v>0.5044445941415184</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.06568171591420424</v>
+        <v>0.5260113201265191</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -1298,332 +1294,332 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998917929082738</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="C3" t="n">
-        <v>3.814362988976479e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999025054365672</v>
+        <v>0.9997835835016291</v>
       </c>
       <c r="E3" t="n">
-        <v>3.436305920243479e-05</v>
+        <v>7.019277779769547e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999100179950515</v>
+        <v>0.9997836064286336</v>
       </c>
       <c r="G3" t="n">
-        <v>9.947206977344203e-05</v>
+        <v>7.017761737132102e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998950052497374</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="I3" t="n">
-        <v>6.873519866439068e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8865656733810553</v>
+        <v>0.4743049775262194</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005322147880907117</v>
+        <v>0.02500552656973925</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9020039096799251</v>
+        <v>0.4629840935543993</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004685498851967715</v>
+        <v>0.02933446351680723</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8663325184399048</v>
+        <v>0.4942980080780141</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006056613095878596</v>
+        <v>0.02926530057637157</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9408129593520325</v>
+        <v>0.4743049775262194</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008526173248019027</v>
+        <v>0.02500552656973925</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8866 ± 0.0053</t>
+          <t>0.4743 ± 0.0250</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.9020 ± 0.0047</t>
+          <t>0.4630 ± 0.0293</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.8663 ± 0.0061</t>
+          <t>0.4943 ± 0.0293</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.9408 ± 0.0085</t>
+          <t>0.4743 ± 0.0250</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.1133261195272185</v>
+        <v>0.525478608290328</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09789859575664217</v>
+        <v>0.5367994899472298</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1335774995551468</v>
+        <v>0.5054855983506195</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05908204589770494</v>
+        <v>0.525478608290328</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998002330614282</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001498252039287662</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9998200033725814</v>
+        <v>0.9992841547250242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001350057549300141</v>
+        <v>0.0001627286981727347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.999835012740364</v>
+        <v>0.9992842278905526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001414792911934868</v>
+        <v>0.000162754435493228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9998050097495124</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001781062259942747</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0002</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8373064757782587</v>
+        <v>0.4896370900615948</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007921202748569733</v>
+        <v>0.01933706660624757</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8574179044210599</v>
+        <v>0.4821509808509704</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006791646007118555</v>
+        <v>0.01803958842635687</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8347593528327172</v>
+        <v>0.5105144512160568</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01018178979785542</v>
+        <v>0.02432410914559052</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8815059247037649</v>
+        <v>0.4896370900615948</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01113081803728929</v>
+        <v>0.01933706660624757</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8373 ± 0.0079</t>
+          <t>0.4896 ± 0.0193</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.8574 ± 0.0068</t>
+          <t>0.4822 ± 0.0180</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8348 ± 0.0102</t>
+          <t>0.5105 ± 0.0243</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8815 ± 0.0111</t>
+          <t>0.4896 ± 0.0193</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.1624937572831695</v>
+        <v>0.5096470784085235</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1424020989515214</v>
+        <v>0.5171331738740538</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1650756599076468</v>
+        <v>0.4887697766744958</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1182990850457475</v>
+        <v>0.5096470784085235</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9993757283169635</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001870501502766885</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9994375376797811</v>
+        <v>0.9990677568858726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001685162263673175</v>
+        <v>0.0001608208752413142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9994300667201221</v>
+        <v>0.9990678043284467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002203628791389911</v>
+        <v>0.0001608257005270377</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9994450277486123</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001649917504124697</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.8545446978525055</v>
+        <v>0.503046445813218</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006035774246015561</v>
+        <v>0.01411225394044629</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8658002442902049</v>
+        <v>0.5011974866405834</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005834059766358549</v>
+        <v>0.01434134111795885</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8870320336820333</v>
+        <v>0.5175084335707233</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006014897645580653</v>
+        <v>0.01570864663975971</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8456127193640318</v>
+        <v>0.503046445813218</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008646661109252191</v>
+        <v>0.01411225394044629</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8545 ± 0.0060</t>
+          <t>0.5030 ± 0.0141</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8658 ± 0.0058</t>
+          <t>0.5012 ± 0.0143</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8870 ± 0.0060</t>
+          <t>0.5175 ± 0.0157</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8456 ± 0.0086</t>
+          <t>0.5030 ± 0.0141</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.144831030464458</v>
+        <v>0.4960213084734475</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1336372933895762</v>
+        <v>0.4978702702452892</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1123980330380888</v>
+        <v>0.4815593707577234</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1538323083845805</v>
+        <v>0.4960213084734475</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -1634,108 +1630,108 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9430830697519561</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003054622010995107</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9486269064274188</v>
+        <v>0.9425705685761205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002733229331666377</v>
+        <v>0.00466313192865296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9503557108620792</v>
+        <v>0.9427724657852593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004797011192999022</v>
+        <v>0.004363449095413103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9469326533673316</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004340358980694475</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9431 ± 0.0031</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9486 ± 0.0027</t>
+          <t>0.9426 ± 0.0047</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9504 ± 0.0048</t>
+          <t>0.9428 ± 0.0044</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9469 ± 0.0043</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.7802896620609289</v>
+        <v>0.4709006159480606</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02365755075624813</v>
+        <v>0.03258625129991426</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8034912472240883</v>
+        <v>0.4664137722971103</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02117157621373452</v>
+        <v>0.03312449391266216</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7978041374525189</v>
+        <v>0.4834117330807893</v>
       </c>
       <c r="S6" t="n">
-        <v>0.022863200634055</v>
+        <v>0.03256688899790051</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8095845207739613</v>
+        <v>0.4709006159480606</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02531687241731768</v>
+        <v>0.03258625129991426</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.7803 ± 0.0237</t>
+          <t>0.4709 ± 0.0326</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.8035 ± 0.0212</t>
+          <t>0.4664 ± 0.0331</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0229</t>
+          <t>0.4834 ± 0.0326</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8096 ± 0.0253</t>
+          <t>0.4709 ± 0.0326</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.1627934076910272</v>
+        <v>0.4716414183452638</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1451356592033305</v>
+        <v>0.4761567962790103</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1525515734095603</v>
+        <v>0.45936073270447</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1373481325933703</v>
+        <v>0.4716414183452638</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -1746,332 +1742,332 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8177376394206759</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009463270545125387</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8351441635674031</v>
+        <v>0.8247088934359363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009911515687219402</v>
+        <v>0.003892267554784565</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8380774142407716</v>
+        <v>0.8247249436711384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007023800154772467</v>
+        <v>0.003908421972607685</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8324883755812209</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01907263019534354</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0095</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8351 ± 0.0099</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8381 ± 0.0070</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8325 ± 0.0191</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.7879473947061761</v>
+        <v>0.4647577825869819</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01187750298864832</v>
+        <v>0.04178473572158246</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8152343871639589</v>
+        <v>0.4498948207827117</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0126440930466092</v>
+        <v>0.05042214133867078</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7887885942352234</v>
+        <v>0.4829826334510738</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006890938677445141</v>
+        <v>0.043966958611615</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8438878056097195</v>
+        <v>0.4647577825869819</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02446228235832</v>
+        <v>0.04178473572158245</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.7879 ± 0.0119</t>
+          <t>0.4648 ± 0.0418</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8152 ± 0.0126</t>
+          <t>0.4499 ± 0.0504</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.7888 ± 0.0069</t>
+          <t>0.4830 ± 0.0440</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.8439 ± 0.0245</t>
+          <t>0.4648 ± 0.0418</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.02979024471449976</v>
+        <v>0.3599716996837022</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01990977640344416</v>
+        <v>0.3748140726532246</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04928882000554824</v>
+        <v>0.3417423102200646</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01139943002849864</v>
+        <v>0.3599716996837022</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6532711836191111</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003432765231763527</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7102051701755642</v>
+        <v>0.6593911279336568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002525563014958159</v>
+        <v>0.006146935199587473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6622882541511838</v>
+        <v>0.6671002535150103</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003196371629185143</v>
+        <v>0.005616591844606063</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7656067196640167</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002835651757146686</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.6533 ± 0.0034</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7102 ± 0.0025</t>
+          <t>0.6594 ± 0.0061</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.6623 ± 0.0032</t>
+          <t>0.6671 ± 0.0056</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.7656 ± 0.0028</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.6629432328949559</v>
+        <v>0.4567920759114367</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00567524574843845</v>
+        <v>0.02385719374993779</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6987984491408717</v>
+        <v>0.375047678188112</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005611616993817419</v>
+        <v>0.06793533042103246</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6931200354970773</v>
+        <v>0.4831790677481614</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005281692239706439</v>
+        <v>0.05295597856343923</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7046197690115493</v>
+        <v>0.4567920759114367</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00835231995919257</v>
+        <v>0.02385719374993779</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.6629 ± 0.0057</t>
+          <t>0.4568 ± 0.0239</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.6988 ± 0.0056</t>
+          <t>0.3750 ± 0.0679</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.6931 ± 0.0053</t>
+          <t>0.4832 ± 0.0530</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.7046 ± 0.0084</t>
+          <t>0.4568 ± 0.0239</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>-0.009672049275844863</v>
+        <v>0.2016730481105377</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01140672103469242</v>
+        <v>0.2843434497455449</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.03083178134589359</v>
+        <v>0.1839211857668489</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0609869506524674</v>
+        <v>0.2016730481105377</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6530214749458965</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009110561236368791</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6586554205410092</v>
+        <v>0.6487666462408367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01000642657450882</v>
+        <v>0.0007010223627725054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7262195138345482</v>
+        <v>0.653007104192831</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02162521657245883</v>
+        <v>0.0006802190230959388</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6036898155092245</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02328275950044984</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.6530 ± 0.0091</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.6587 ± 0.0100</t>
+          <t>0.6488 ± 0.0007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.7262 ± 0.0216</t>
+          <t>0.6530 ± 0.0007</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.6037 ± 0.0233</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.6569668719826869</v>
+        <v>0.490086565673381</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0109464844492528</v>
+        <v>0.008321074097074539</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7054501163275078</v>
+        <v>0.4791353506168876</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.005909802092955805</v>
+        <v>0.01800807311241995</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6749553590245572</v>
+        <v>0.5113217560724342</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02014059479190419</v>
+        <v>0.01485061249722588</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7405129743512825</v>
+        <v>0.490086565673381</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02783700788809631</v>
+        <v>0.008321074097074539</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.6570 ± 0.0109</t>
+          <t>0.4901 ± 0.0083</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.7055 ± 0.0059</t>
+          <t>0.4791 ± 0.0180</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.6750 ± 0.0201</t>
+          <t>0.5113 ± 0.0149</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.7405 ± 0.0278</t>
+          <t>0.4901 ± 0.0083</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.003945397036790421</v>
+        <v>0.1649492259031131</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.04679469578649853</v>
+        <v>0.1696312956239491</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05126415480999102</v>
+        <v>0.1416853481203968</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.136823158842058</v>
+        <v>0.1649492259031131</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -2082,108 +2078,108 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.652688530048277</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003540466283100108</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7111657290688942</v>
+        <v>0.6472491388140823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002515858645437491</v>
+        <v>0.0008797666050638595</v>
       </c>
       <c r="F10" t="n">
-        <v>0.660338278612806</v>
+        <v>0.6522410581225434</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003326244875037613</v>
+        <v>0.0008659629294319769</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7704814759262038</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002684656261806534</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.6527 ± 0.0035</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.7112 ± 0.0025</t>
+          <t>0.6472 ± 0.0009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0033</t>
+          <t>0.6522 ± 0.0009</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.7705 ± 0.0027</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.6626602297319792</v>
+        <v>0.4904694523056434</v>
       </c>
       <c r="O10" t="n">
-        <v>0.005627384388638883</v>
+        <v>0.008326789438753403</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6988185941478678</v>
+        <v>0.4795696637377163</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.005350444122233014</v>
+        <v>0.01809438698815296</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6925340588965098</v>
+        <v>0.5115524717956739</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005459372229371497</v>
+        <v>0.01472834362975949</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7052647367631618</v>
+        <v>0.4904694523056434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007750128605416733</v>
+        <v>0.008326789438753403</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.6627 ± 0.0056</t>
+          <t>0.4905 ± 0.0083</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.6988 ± 0.0054</t>
+          <t>0.4796 ± 0.0181</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.6925 ± 0.0055</t>
+          <t>0.5116 ± 0.0147</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.7053 ± 0.0078</t>
+          <t>0.4905 ± 0.0083</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>-0.009971699683702262</v>
+        <v>0.1636507408023972</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01234713492102635</v>
+        <v>0.167679475076366</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03219578028370373</v>
+        <v>0.1406885863268695</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06521673916304194</v>
+        <v>0.1636507408023972</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -2194,108 +2190,108 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6093557516231064</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002206246746399765</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5471586204572338</v>
+        <v>0.5949230921311406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003948342675541275</v>
+        <v>0.001724225896607475</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7669376693867336</v>
+        <v>0.6638581767391858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002744162729666706</v>
+        <v>0.002274716056977206</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4253037348132593</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004574279456311722</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.6094 ± 0.0022</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.5472 ± 0.0039</t>
+          <t>0.5949 ± 0.0017</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7669 ± 0.0027</t>
+          <t>0.6639 ± 0.0023</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.4253 ± 0.0046</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.5940069918428501</v>
+        <v>0.4396121191942733</v>
       </c>
       <c r="O11" t="n">
-        <v>0.004325593662813265</v>
+        <v>0.005929765607203967</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5258634247519973</v>
+        <v>0.3158371749202116</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.007877054735555529</v>
+        <v>0.03205890910700934</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7471363260614226</v>
+        <v>0.430789806731939</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007472677631446342</v>
+        <v>0.04058317794692768</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4058047097645117</v>
+        <v>0.4396121191942733</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009362764476637342</v>
+        <v>0.005929765607203967</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.5940 ± 0.0043</t>
+          <t>0.4396 ± 0.0059</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.5259 ± 0.0079</t>
+          <t>0.3158 ± 0.0321</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.7471 ± 0.0075</t>
+          <t>0.4308 ± 0.0406</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.4058 ± 0.0094</t>
+          <t>0.4396 ± 0.0059</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.01534875978025629</v>
+        <v>0.1686948560013318</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02129519570523652</v>
+        <v>0.279085917210929</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01980134332531103</v>
+        <v>0.2330683700072468</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01949902504874756</v>
+        <v>0.1686948560013318</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -2306,16 +2302,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.999983352755119</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>3.329448976194804e-05</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9999849996249907</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>3.000075001873271e-05</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
@@ -2324,10 +2320,10 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9999700014999249</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.999700014998055e-05</v>
+        <v>0</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -2346,68 +2342,68 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.0000 ± 0.0001</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.4556517396370901</v>
+        <v>0.9117279840186449</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01505916985844268</v>
+        <v>0.005456788953133809</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5251324138567903</v>
+        <v>0.9115328861296605</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02965203013303199</v>
+        <v>0.005493089449726255</v>
       </c>
       <c r="R12" t="n">
-        <v>0.508293849138358</v>
+        <v>0.9119791375656241</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01220628429477217</v>
+        <v>0.005468346973052841</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5448927553622319</v>
+        <v>0.9117279840186449</v>
       </c>
       <c r="U12" t="n">
-        <v>0.05282670278344706</v>
+        <v>0.005456788953133809</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.4557 ± 0.0151</t>
+          <t>0.9117 ± 0.0055</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.5251 ± 0.0297</t>
+          <t>0.9115 ± 0.0055</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0.5083 ± 0.0122</t>
+          <t>0.9120 ± 0.0055</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>0.5449 ± 0.0528</t>
+          <t>0.9117 ± 0.0055</t>
         </is>
       </c>
       <c r="Z12" t="n">
-        <v>0.5443316131180289</v>
+        <v>0.08827201598135515</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.4748525857682003</v>
+        <v>0.08846711387033945</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.491706150861642</v>
+        <v>0.0880208624343759</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.455077246137693</v>
+        <v>0.08827201598135515</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -2418,332 +2414,332 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9998917929082738</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="C13" t="n">
-        <v>3.814362988976479e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9999025054365672</v>
+        <v>0.9997835835016291</v>
       </c>
       <c r="E13" t="n">
-        <v>3.436305920243479e-05</v>
+        <v>7.019277779769547e-05</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9999100179950515</v>
+        <v>0.9997836064286336</v>
       </c>
       <c r="G13" t="n">
-        <v>9.947206977344203e-05</v>
+        <v>7.017761737132102e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9998950052497374</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="I13" t="n">
-        <v>6.873519866439068e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.4495172298984518</v>
+        <v>0.8210920592641917</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02139291607747043</v>
+        <v>0.006780014991371465</v>
       </c>
       <c r="P13" t="n">
-        <v>0.5120664063038667</v>
+        <v>0.8210449560123243</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03596609091386745</v>
+        <v>0.006911054843633828</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5027788184560051</v>
+        <v>0.8214476742758514</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01709804903862116</v>
+        <v>0.0077601479665146</v>
       </c>
       <c r="T13" t="n">
-        <v>0.523638818059097</v>
+        <v>0.8210920592641917</v>
       </c>
       <c r="U13" t="n">
-        <v>0.06097158979582164</v>
+        <v>0.006780014991371465</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0.4495 ± 0.0214</t>
+          <t>0.8211 ± 0.0068</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0.5121 ± 0.0360</t>
+          <t>0.8210 ± 0.0069</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0.5028 ± 0.0171</t>
+          <t>0.8214 ± 0.0078</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0.5236 ± 0.0610</t>
+          <t>0.8211 ± 0.0068</t>
         </is>
       </c>
       <c r="Z13" t="n">
-        <v>0.550374563009822</v>
+        <v>0.1786915265523557</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4878360991327005</v>
+        <v>0.1787386274893048</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.4971311995390464</v>
+        <v>0.1783359321527822</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.4762561871906404</v>
+        <v>0.1786915265523557</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9998002330614282</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0001498252039287662</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9998200033725814</v>
+        <v>0.9992841547250242</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0001350057549300141</v>
+        <v>0.0001627286981727347</v>
       </c>
       <c r="F14" t="n">
-        <v>0.999835012740364</v>
+        <v>0.9992842278905526</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0001414792911934868</v>
+        <v>0.000162754435493228</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9998050097495124</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0001781062259942747</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0002</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.4774346595638422</v>
+        <v>0.8418594972532046</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01317277090397607</v>
+        <v>0.006024198380485434</v>
       </c>
       <c r="P14" t="n">
-        <v>0.532965592982555</v>
+        <v>0.8415686356574531</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02309132836844926</v>
+        <v>0.006118992614634194</v>
       </c>
       <c r="R14" t="n">
-        <v>0.5283299879552034</v>
+        <v>0.8417131512620616</v>
       </c>
       <c r="S14" t="n">
-        <v>0.01015192567167587</v>
+        <v>0.006025191415431225</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5387730613469327</v>
+        <v>0.8418594972532046</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04045400898828645</v>
+        <v>0.006024198380485434</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.4774 ± 0.0132</t>
+          <t>0.8419 ± 0.0060</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.5330 ± 0.0231</t>
+          <t>0.8416 ± 0.0061</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.5283 ± 0.0102</t>
+          <t>0.8417 ± 0.0060</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.5388 ± 0.0405</t>
+          <t>0.8419 ± 0.0060</t>
         </is>
       </c>
       <c r="Z14" t="n">
-        <v>0.5223655734975861</v>
+        <v>0.1574246712169137</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.4668544103900264</v>
+        <v>0.1577155190675711</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.4715050247851607</v>
+        <v>0.157571076628491</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.4610319484025797</v>
+        <v>0.1574246712169137</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9993757283169635</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001870501502766885</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9994375376797811</v>
+        <v>0.9990677568858726</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0001685162263673175</v>
+        <v>0.0001608208752413142</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9994300667201221</v>
+        <v>0.9990678043284467</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0002203628791389911</v>
+        <v>0.0001608257005270377</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9994450277486123</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001649917504124697</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.4854752788413517</v>
+        <v>0.8329282503745631</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01105508989160575</v>
+        <v>0.008690453568021311</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5406892133463262</v>
+        <v>0.8315537471947743</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01837093492391009</v>
+        <v>0.009155054107192502</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5355723318112794</v>
+        <v>0.8345785199048514</v>
       </c>
       <c r="S15" t="n">
-        <v>0.009172088815241492</v>
+        <v>0.00792244751737179</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5466776661166942</v>
+        <v>0.8329282503745631</v>
       </c>
       <c r="U15" t="n">
-        <v>0.03266208874412134</v>
+        <v>0.008690453568021311</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.4855 ± 0.0111</t>
+          <t>0.8329 ± 0.0087</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.5407 ± 0.0184</t>
+          <t>0.8316 ± 0.0092</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.5356 ± 0.0092</t>
+          <t>0.8346 ± 0.0079</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.5467 ± 0.0327</t>
+          <t>0.8329 ± 0.0087</t>
         </is>
       </c>
       <c r="Z15" t="n">
-        <v>0.5139004494756119</v>
+        <v>0.1661395039121024</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.4587483243334548</v>
+        <v>0.1675140096910983</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.4638577349088427</v>
+        <v>0.1644892844235952</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4527673616319181</v>
+        <v>0.1661395039121024</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -2754,108 +2750,108 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9430830697519561</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="C16" t="n">
-        <v>0.003054622010995107</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9486269064274188</v>
+        <v>0.9425705685761205</v>
       </c>
       <c r="E16" t="n">
-        <v>0.002733229331666377</v>
+        <v>0.00466313192865296</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9503557108620792</v>
+        <v>0.9427724657852593</v>
       </c>
       <c r="G16" t="n">
-        <v>0.004797011192999022</v>
+        <v>0.004363449095413103</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9469326533673316</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="I16" t="n">
-        <v>0.004340358980694475</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.9431 ± 0.0031</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.9486 ± 0.0027</t>
+          <t>0.9426 ± 0.0047</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0.9504 ± 0.0048</t>
+          <t>0.9428 ± 0.0044</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>0.9469 ± 0.0043</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.4905859830198102</v>
+        <v>0.7628683202929916</v>
       </c>
       <c r="O16" t="n">
-        <v>0.03061241057693206</v>
+        <v>0.02162214626961341</v>
       </c>
       <c r="P16" t="n">
-        <v>0.537626157168307</v>
+        <v>0.7625153419223542</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04062901712061393</v>
+        <v>0.02252279067347974</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5409967231367535</v>
+        <v>0.7640201225447635</v>
       </c>
       <c r="S16" t="n">
-        <v>0.02728335831242973</v>
+        <v>0.02290228574001787</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5367181640917955</v>
+        <v>0.7628683202929916</v>
       </c>
       <c r="U16" t="n">
-        <v>0.05949013622880233</v>
+        <v>0.02162214626961341</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>0.4906 ± 0.0306</t>
+          <t>0.7629 ± 0.0216</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.5376 ± 0.0406</t>
+          <t>0.7625 ± 0.0225</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>0.5410 ± 0.0273</t>
+          <t>0.7640 ± 0.0229</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>0.5367 ± 0.0595</t>
+          <t>0.7629 ± 0.0216</t>
         </is>
       </c>
       <c r="Z16" t="n">
-        <v>0.4524970867321459</v>
+        <v>0.1796737140003328</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4110007492591118</v>
+        <v>0.1800552266537664</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.4093589877253256</v>
+        <v>0.1787523432404958</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.4102144892755361</v>
+        <v>0.1796737140003328</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -2866,332 +2862,332 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8177376394206759</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="C17" t="n">
-        <v>0.009463270545125387</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8351441635674031</v>
+        <v>0.8247088934359363</v>
       </c>
       <c r="E17" t="n">
-        <v>0.009911515687219402</v>
+        <v>0.003892267554784565</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8380774142407716</v>
+        <v>0.8247249436711384</v>
       </c>
       <c r="G17" t="n">
-        <v>0.007023800154772467</v>
+        <v>0.003908421972607685</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8324883755812209</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01907263019534354</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0095</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.8351 ± 0.0099</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.8381 ± 0.0070</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.8325 ± 0.0191</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.4827201598135508</v>
+        <v>0.7552688530048278</v>
       </c>
       <c r="O17" t="n">
-        <v>0.018763379920189</v>
+        <v>0.01228916760864686</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5697167428891527</v>
+        <v>0.7551959459542747</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.03232527873997269</v>
+        <v>0.01263995609332125</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5283304352657389</v>
+        <v>0.755744437774852</v>
       </c>
       <c r="S17" t="n">
-        <v>0.01280385704440608</v>
+        <v>0.01316604194496796</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6208339583020848</v>
+        <v>0.7552688530048278</v>
       </c>
       <c r="U17" t="n">
-        <v>0.06568566855493009</v>
+        <v>0.01228916760864686</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.4827 ± 0.0188</t>
+          <t>0.7553 ± 0.0123</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.5697 ± 0.0323</t>
+          <t>0.7552 ± 0.0126</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.5283 ± 0.0128</t>
+          <t>0.7557 ± 0.0132</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.6208 ± 0.0657</t>
+          <t>0.7553 ± 0.0123</t>
         </is>
       </c>
       <c r="Z17" t="n">
-        <v>0.3350174796071251</v>
+        <v>0.06946062926585628</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.2654274206782503</v>
+        <v>0.06951294748166159</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.3097469789750328</v>
+        <v>0.06898050589628635</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.2116544172791361</v>
+        <v>0.06946062926585628</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6532711836191111</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="C18" t="n">
-        <v>0.003432765231763527</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7102051701755642</v>
+        <v>0.6593911279336568</v>
       </c>
       <c r="E18" t="n">
-        <v>0.002525563014958159</v>
+        <v>0.006146935199587473</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6622882541511838</v>
+        <v>0.6671002535150103</v>
       </c>
       <c r="G18" t="n">
-        <v>0.003196371629185143</v>
+        <v>0.005616591844606063</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7656067196640167</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="I18" t="n">
-        <v>0.002835651757146686</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.6533 ± 0.0034</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0.7102 ± 0.0025</t>
+          <t>0.6594 ± 0.0061</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0.6623 ± 0.0032</t>
+          <t>0.6671 ± 0.0056</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>0.7656 ± 0.0028</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.5085983019810223</v>
+        <v>0.6644248376893623</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01367199263763621</v>
+        <v>0.01420251642324667</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5999205800676521</v>
+        <v>0.6604921508095692</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02213500022359702</v>
+        <v>0.01922134090421259</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5469010613505055</v>
+        <v>0.6639717503612725</v>
       </c>
       <c r="S18" t="n">
-        <v>0.009478453950554485</v>
+        <v>0.01411242551291257</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6659217039148043</v>
+        <v>0.6644248376893623</v>
       </c>
       <c r="U18" t="n">
-        <v>0.04799516502372499</v>
+        <v>0.01420251642324667</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>0.5086 ± 0.0137</t>
+          <t>0.6644 ± 0.0142</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.5999 ± 0.0221</t>
+          <t>0.6605 ± 0.0192</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>0.5469 ± 0.0095</t>
+          <t>0.6640 ± 0.0141</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>0.6659 ± 0.0480</t>
+          <t>0.6644 ± 0.0142</t>
         </is>
       </c>
       <c r="Z18" t="n">
-        <v>0.1446728816380888</v>
+        <v>-0.005959713667388011</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.110284590107912</v>
+        <v>-0.001101022875912405</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.1153871928006782</v>
+        <v>0.003128503153737805</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.0996850157492124</v>
+        <v>-0.005959713667388011</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6530214749458965</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="C19" t="n">
-        <v>0.009110561236368791</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6586554205410092</v>
+        <v>0.6487666462408367</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01000642657450882</v>
+        <v>0.0007010223627725054</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7262195138345482</v>
+        <v>0.653007104192831</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02162521657245883</v>
+        <v>0.0006802190230959388</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6036898155092245</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="I19" t="n">
-        <v>0.02328275950044984</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.6530 ± 0.0091</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.6587 ± 0.0100</t>
+          <t>0.6488 ± 0.0007</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.7262 ± 0.0216</t>
+          <t>0.6530 ± 0.0007</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.6037 ± 0.0233</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.4825703346096221</v>
+        <v>0.6522723489262526</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01330375279247198</v>
+        <v>0.003209173564452282</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5632326588237714</v>
+        <v>0.6447246870404532</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.03500931331399579</v>
+        <v>0.00393454619998641</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5292177139210736</v>
+        <v>0.6505522631114936</v>
       </c>
       <c r="S19" t="n">
-        <v>0.009308951685638384</v>
+        <v>0.003235900172279906</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6064196790160492</v>
+        <v>0.6522723489262526</v>
       </c>
       <c r="U19" t="n">
-        <v>0.07512839714970289</v>
+        <v>0.003209173564452282</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.4826 ± 0.0133</t>
+          <t>0.6523 ± 0.0032</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.5632 ± 0.0350</t>
+          <t>0.6447 ± 0.0039</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.5292 ± 0.0093</t>
+          <t>0.6506 ± 0.0032</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.6064 ± 0.0751</t>
+          <t>0.6523 ± 0.0032</t>
         </is>
       </c>
       <c r="Z19" t="n">
-        <v>0.1704511403362744</v>
+        <v>0.002763442650241421</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.09542276171723785</v>
+        <v>0.004041959200383527</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.1970017999134746</v>
+        <v>0.002454841081337422</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.002729863506824692</v>
+        <v>0.002763442650241421</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -3202,108 +3198,108 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.652688530048277</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="C20" t="n">
-        <v>0.003540466283100108</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7111657290688942</v>
+        <v>0.6472491388140823</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002515858645437491</v>
+        <v>0.0008797666050638595</v>
       </c>
       <c r="F20" t="n">
-        <v>0.660338278612806</v>
+        <v>0.6522410581225434</v>
       </c>
       <c r="G20" t="n">
-        <v>0.003326244875037613</v>
+        <v>0.0008659629294319769</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7704814759262038</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="I20" t="n">
-        <v>0.002684656261806534</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.6527 ± 0.0035</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.7112 ± 0.0025</t>
+          <t>0.6472 ± 0.0009</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0033</t>
+          <t>0.6522 ± 0.0009</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.7705 ± 0.0027</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.5084984185117364</v>
+        <v>0.6489512235724987</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01407019435272617</v>
+        <v>0.003448308891968959</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5991782477315457</v>
+        <v>0.6407123832623596</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02241384616919643</v>
+        <v>0.004257906132352384</v>
       </c>
       <c r="R20" t="n">
-        <v>0.5469659598092009</v>
+        <v>0.6472549050774413</v>
       </c>
       <c r="S20" t="n">
-        <v>0.00985408369532533</v>
+        <v>0.003508859648006634</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6640167991600421</v>
+        <v>0.6489512235724987</v>
       </c>
       <c r="U20" t="n">
-        <v>0.04816324349956423</v>
+        <v>0.003448308891968959</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.5085 ± 0.0141</t>
+          <t>0.6490 ± 0.0034</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.5992 ± 0.0224</t>
+          <t>0.6407 ± 0.0043</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.5470 ± 0.0099</t>
+          <t>0.6473 ± 0.0035</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.6640 ± 0.0482</t>
+          <t>0.6490 ± 0.0034</t>
         </is>
       </c>
       <c r="Z20" t="n">
-        <v>0.1441901115365406</v>
+        <v>0.005168969535541912</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1119874813373485</v>
+        <v>0.006536755551722728</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.1133723188036051</v>
+        <v>0.004986153045102082</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.1064646767661617</v>
+        <v>0.005168969535541912</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -3314,108 +3310,108 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6093557516231064</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="C21" t="n">
-        <v>0.002206246746399765</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5471586204572338</v>
+        <v>0.5949230921311406</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003948342675541275</v>
+        <v>0.001724225896607475</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7669376693867336</v>
+        <v>0.6638581767391858</v>
       </c>
       <c r="G21" t="n">
-        <v>0.002744162729666706</v>
+        <v>0.002274716056977206</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4253037348132593</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="I21" t="n">
-        <v>0.004574279456311722</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.6094 ± 0.0022</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.5472 ± 0.0039</t>
+          <t>0.5949 ± 0.0017</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.7669 ± 0.0027</t>
+          <t>0.6639 ± 0.0023</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.4253 ± 0.0046</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.5128849675378724</v>
+        <v>0.6096221075412019</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0129711738548142</v>
+        <v>0.005555459405745213</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6408896636018478</v>
+        <v>0.5970035031909664</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02136845704392922</v>
+        <v>0.008812614470602671</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5421369235868775</v>
+        <v>0.6631691510212023</v>
       </c>
       <c r="S21" t="n">
-        <v>0.007397371420856608</v>
+        <v>0.006165808303471135</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7862906854657268</v>
+        <v>0.6096221075412019</v>
       </c>
       <c r="U21" t="n">
-        <v>0.06096997914441964</v>
+        <v>0.005555459405745213</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.5129 ± 0.0130</t>
+          <t>0.6096 ± 0.0056</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.6409 ± 0.0214</t>
+          <t>0.5970 ± 0.0088</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.5421 ± 0.0074</t>
+          <t>0.6632 ± 0.0062</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.7863 ± 0.0610</t>
+          <t>0.6096 ± 0.0056</t>
         </is>
       </c>
       <c r="Z21" t="n">
-        <v>0.09647078408523402</v>
+        <v>-0.00131513234559677</v>
       </c>
       <c r="AA21" t="n">
-        <v>-0.093731043144614</v>
+        <v>-0.002080411059825815</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.2248007457998561</v>
+        <v>0.0006890257179834602</v>
       </c>
       <c r="AC21" t="n">
-        <v>-0.3609869506524675</v>
+        <v>-0.00131513234559677</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -3467,16 +3463,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06909938405193941</v>
+        <v>0.08403196271017147</v>
       </c>
       <c r="C2" t="n">
-        <v>0.06138362605417576</v>
+        <v>0.08494007250701097</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07081415927830575</v>
+        <v>0.08474085277741873</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05317234138293078</v>
+        <v>0.08403196271017147</v>
       </c>
     </row>
     <row r="3">
@@ -3486,16 +3482,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3474271683036457</v>
+        <v>0.3587739304145164</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2788683379579628</v>
+        <v>0.3840214666151817</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3293868134112664</v>
+        <v>0.3480725873070253</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2309434528273585</v>
+        <v>0.3587739304145164</v>
       </c>
     </row>
   </sheetData>
@@ -3509,7 +3505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3661,6 +3657,1126 @@
       <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ExtraTrees</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1.0000 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1.0000 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>1.0000 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.0000 ± 0.0000</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>0.4739886798734809</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0111696720982644</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.4632992745037796</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.007614526669208086</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.4955554058584816</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.01923946767949742</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.4739886798734809</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.0111696720982644</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.4740 ± 0.0112</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.4633 ± 0.0076</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.4956 ± 0.0192</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.4740 ± 0.0112</t>
+        </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.5260113201265191</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5367007254962204</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5044445941415184</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.5260113201265191</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RandomForest</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.9997835858165474</v>
+      </c>
+      <c r="C3" t="n">
+        <v>7.019094745394207e-05</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9997835835016291</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7.019277779769547e-05</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9997836064286336</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.017761737132102e-05</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.9997835858165474</v>
+      </c>
+      <c r="I3" t="n">
+        <v>7.019094745394207e-05</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9998 ± 0.0001</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.9998 ± 0.0001</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.9998 ± 0.0001</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.9998 ± 0.0001</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>0.4743049775262194</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.02500552656973925</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.4629840935543993</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.02933446351680723</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.4942980080780141</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.02926530057637157</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.4743049775262194</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.02500552656973925</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.4743 ± 0.0250</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.4630 ± 0.0293</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.4943 ± 0.0293</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.4743 ± 0.0250</t>
+        </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.525478608290328</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.5367994899472298</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.5054855983506195</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.525478608290328</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.9992841684701184</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0001627310171312947</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9992841547250242</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.0001627286981727347</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9992842278905526</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.000162754435493228</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9992841684701184</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0001627310171312947</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9993 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9993 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9993 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.9993 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4896370900615948</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.01933706660624757</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4821509808509704</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.01803958842635687</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5105144512160568</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.02432410914559052</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.4896370900615948</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01933706660624757</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.4896 ± 0.0193</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.4822 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.5105 ± 0.0243</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.4896 ± 0.0193</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.5096470784085235</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.5171331738740538</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4887697766744958</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.5096470784085235</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MLP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.9990677542866655</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0001608276649041787</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9990677568858726</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.0001608208752413142</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9990678043284467</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0001608257005270377</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9990677542866655</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.0001608276649041787</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.9991 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.9991 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.9991 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.9991 ± 0.0002</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>0.503046445813218</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.01411225394044629</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5011974866405834</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.01434134111795885</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5175084335707233</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.01570864663975971</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.503046445813218</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.01411225394044629</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.5030 ± 0.0141</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.5012 ± 0.0143</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.5175 ± 0.0157</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.5030 ± 0.0141</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.4960213084734475</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4978702702452892</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.4815593707577234</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4960213084734475</v>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DecisionTree</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9425420342933244</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.004713462253088096</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9425705685761205</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.00466313192865296</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9427724657852593</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.004363449095413103</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9425420342933244</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.004713462253088096</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.9425 ± 0.0047</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.9426 ± 0.0047</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.9428 ± 0.0044</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.9425 ± 0.0047</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4709006159480606</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.03258625129991426</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4664137722971103</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.03312449391266216</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.4834117330807893</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.03256688899790051</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4709006159480606</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.03258625129991426</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.4709 ± 0.0326</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.4664 ± 0.0331</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.4834 ± 0.0326</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.4709 ± 0.0326</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4716414183452638</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.4761567962790103</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.45936073270447</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.4716414183452638</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GradientBoost</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8247294822706841</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.003881194856963221</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8247088934359363</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.003892267554784565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8247249436711384</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.003908421972607685</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8247294822706841</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.003881194856963221</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.8247 ± 0.0039</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.8247 ± 0.0039</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8247 ± 0.0039</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8247 ± 0.0039</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>0.4647577825869819</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.04178473572158246</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.4498948207827117</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.05042214133867078</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4829826334510738</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.043966958611615</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.4647577825869819</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.04178473572158245</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.4648 ± 0.0418</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.4499 ± 0.0504</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.4830 ± 0.0440</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.4648 ± 0.0418</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.3599716996837022</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.3748140726532246</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.3417423102200646</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.3599716996837022</v>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AdaBoost</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6584651240219743</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.006118953967439291</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.6593911279336568</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.006146935199587473</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6671002535150103</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.005616591844606063</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6584651240219743</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.006118953967439291</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.6585 ± 0.0061</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.6594 ± 0.0061</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.6671 ± 0.0056</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.6585 ± 0.0061</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4567920759114367</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.02385719374993779</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.375047678188112</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.06793533042103246</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4831790677481614</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.05295597856343923</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.4567920759114367</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.02385719374993779</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.4568 ± 0.0239</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.3750 ± 0.0679</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.4832 ± 0.0530</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.4568 ± 0.0239</t>
+        </is>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.2016730481105377</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.2843434497455449</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.1839211857668489</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.2016730481105377</v>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>LogReg</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.6550357915764941</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0006532850631046708</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.6487666462408367</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.0007010223627725054</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.653007104192831</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0006802190230959388</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.6550357915764941</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0006532850631046708</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.6550 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.6488 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.6530 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.6550 ± 0.0007</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>0.490086565673381</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.008321074097074539</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4791353506168876</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01800807311241995</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5113217560724342</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01485061249722588</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.490086565673381</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.008321074097074539</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.4901 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.4791 ± 0.0180</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.5113 ± 0.0149</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.4901 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.1649492259031131</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.1696312956239491</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1416853481203968</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.1649492259031131</v>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SVM-RBF</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6541201931080406</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0008269807351539551</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6472491388140823</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.0008797666050638595</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.6522410581225434</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0008659629294319769</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6541201931080406</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.0008269807351539551</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.6541 ± 0.0008</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.6472 ± 0.0009</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.6522 ± 0.0009</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.6541 ± 0.0008</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4904694523056434</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.008326789438753403</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.4795696637377163</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01809438698815296</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5115524717956739</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01472834362975949</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4904694523056434</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.008326789438753403</v>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.4905 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.4796 ± 0.0181</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.5116 ± 0.0147</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.4905 ± 0.0083</t>
+        </is>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.1636507408023972</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.167679475076366</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.1406885863268695</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.1636507408023972</v>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>NaiveBayes</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.6083069751956052</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.001551660554614313</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5949230921311406</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.001724225896607475</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6638581767391858</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.002274716056977206</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6083069751956052</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.001551660554614313</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.6083 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.5949 ± 0.0017</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.6639 ± 0.0023</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.6083 ± 0.0016</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4396121191942733</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.005929765607203967</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.3158371749202116</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.03205890910700934</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.430789806731939</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.04058317794692768</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.4396121191942733</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.005929765607203967</v>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.4396 ± 0.0059</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.3158 ± 0.0321</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.4308 ± 0.0406</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.4396 ± 0.0059</t>
+        </is>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.1686948560013318</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.279085917210929</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.2330683700072468</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1686948560013318</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -3675,504 +4791,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -4335,16 +4953,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.999983352755119</v>
+        <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.329448976194804e-05</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9999849996249907</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>3.000075001873271e-05</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
@@ -4353,10 +4971,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9999700014999249</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.999700014998055e-05</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -4375,64 +4993,64 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>1.0000 ± 0.0001</t>
+          <t>1.0000 ± 0.0000</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.9139836857000165</v>
+        <v>0.9117279840186449</v>
       </c>
       <c r="O2" t="n">
-        <v>0.005142112712232631</v>
+        <v>0.005456788953133809</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9233865186622043</v>
+        <v>0.9115328861296605</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00481176833110665</v>
+        <v>0.005493089449726255</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9127879296386381</v>
+        <v>0.9119791375656241</v>
       </c>
       <c r="S2" t="n">
-        <v>0.004335323832998748</v>
+        <v>0.005468346973052841</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9342882855857206</v>
+        <v>0.9117279840186449</v>
       </c>
       <c r="U2" t="n">
-        <v>0.008863643065170833</v>
+        <v>0.005456788953133809</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.9140 ± 0.0051</t>
+          <t>0.9117 ± 0.0055</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.9234 ± 0.0048</t>
+          <t>0.9115 ± 0.0055</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.9128 ± 0.0043</t>
+          <t>0.9120 ± 0.0055</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.9343 ± 0.0089</t>
+          <t>0.9117 ± 0.0055</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.08599966705510242</v>
+        <v>0.08827201598135515</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.07659848096278632</v>
+        <v>0.08846711387033945</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.08721207036136192</v>
+        <v>0.0880208624343759</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.06568171591420424</v>
+        <v>0.08827201598135515</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -4447,104 +5065,104 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9998917929082738</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="C3" t="n">
-        <v>3.814362988976479e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9999025054365672</v>
+        <v>0.9997835835016291</v>
       </c>
       <c r="E3" t="n">
-        <v>3.436305920243479e-05</v>
+        <v>7.019277779769547e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9999100179950515</v>
+        <v>0.9997836064286336</v>
       </c>
       <c r="G3" t="n">
-        <v>9.947206977344203e-05</v>
+        <v>7.017761737132102e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9998950052497374</v>
+        <v>0.9997835858165474</v>
       </c>
       <c r="I3" t="n">
-        <v>6.873519866439068e-05</v>
+        <v>7.019094745394207e-05</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0000</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.9999 ± 0.0001</t>
+          <t>0.9998 ± 0.0001</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8865656733810553</v>
+        <v>0.8210920592641917</v>
       </c>
       <c r="O3" t="n">
-        <v>0.005322147880907117</v>
+        <v>0.006780014991371465</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9020039096799251</v>
+        <v>0.8210449560123243</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.004685498851967715</v>
+        <v>0.006911054843633828</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8663325184399048</v>
+        <v>0.8214476742758514</v>
       </c>
       <c r="S3" t="n">
-        <v>0.006056613095878596</v>
+        <v>0.0077601479665146</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9408129593520325</v>
+        <v>0.8210920592641917</v>
       </c>
       <c r="U3" t="n">
-        <v>0.008526173248019027</v>
+        <v>0.006780014991371465</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8866 ± 0.0053</t>
+          <t>0.8211 ± 0.0068</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.9020 ± 0.0047</t>
+          <t>0.8210 ± 0.0069</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.8663 ± 0.0061</t>
+          <t>0.8214 ± 0.0078</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.9408 ± 0.0085</t>
+          <t>0.8211 ± 0.0068</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.1133261195272185</v>
+        <v>0.1786915265523557</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.09789859575664217</v>
+        <v>0.1787386274893048</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1335774995551468</v>
+        <v>0.1783359321527822</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.05908204589770494</v>
+        <v>0.1786915265523557</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -4555,108 +5173,108 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9998002330614282</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0001498252039287662</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9998200033725814</v>
+        <v>0.9992841547250242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0001350057549300141</v>
+        <v>0.0001627286981727347</v>
       </c>
       <c r="F4" t="n">
-        <v>0.999835012740364</v>
+        <v>0.9992842278905526</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0001414792911934868</v>
+        <v>0.000162754435493228</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9998050097495124</v>
+        <v>0.9992841684701184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0001781062259942747</v>
+        <v>0.0001627310171312947</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0001</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.9998 ± 0.0002</t>
+          <t>0.9993 ± 0.0002</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8373064757782587</v>
+        <v>0.8418594972532046</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007921202748569733</v>
+        <v>0.006024198380485434</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8574179044210599</v>
+        <v>0.8415686356574531</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.006791646007118555</v>
+        <v>0.006118992614634194</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8347593528327172</v>
+        <v>0.8417131512620616</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01018178979785542</v>
+        <v>0.006025191415431225</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8815059247037649</v>
+        <v>0.8418594972532046</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01113081803728929</v>
+        <v>0.006024198380485434</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8373 ± 0.0079</t>
+          <t>0.8419 ± 0.0060</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.8574 ± 0.0068</t>
+          <t>0.8416 ± 0.0061</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.8348 ± 0.0102</t>
+          <t>0.8417 ± 0.0060</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.8815 ± 0.0111</t>
+          <t>0.8419 ± 0.0060</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.1624937572831695</v>
+        <v>0.1574246712169137</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1424020989515214</v>
+        <v>0.1577155190675711</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.1650756599076468</v>
+        <v>0.157571076628491</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.1182990850457475</v>
+        <v>0.1574246712169137</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -4667,108 +5285,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9993757283169635</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0001870501502766885</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9994375376797811</v>
+        <v>0.9990677568858726</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0001685162263673175</v>
+        <v>0.0001608208752413142</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9994300667201221</v>
+        <v>0.9990678043284467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0002203628791389911</v>
+        <v>0.0001608257005270377</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9994450277486123</v>
+        <v>0.9990677542866655</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0001649917504124697</v>
+        <v>0.0001608276649041787</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.9994 ± 0.0002</t>
+          <t>0.9991 ± 0.0002</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.8545446978525055</v>
+        <v>0.8329282503745631</v>
       </c>
       <c r="O5" t="n">
-        <v>0.006035774246015561</v>
+        <v>0.008690453568021311</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8658002442902049</v>
+        <v>0.8315537471947743</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.005834059766358549</v>
+        <v>0.009155054107192502</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8870320336820333</v>
+        <v>0.8345785199048514</v>
       </c>
       <c r="S5" t="n">
-        <v>0.006014897645580653</v>
+        <v>0.00792244751737179</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8456127193640318</v>
+        <v>0.8329282503745631</v>
       </c>
       <c r="U5" t="n">
-        <v>0.008646661109252191</v>
+        <v>0.008690453568021311</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8545 ± 0.0060</t>
+          <t>0.8329 ± 0.0087</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.8658 ± 0.0058</t>
+          <t>0.8316 ± 0.0092</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.8870 ± 0.0060</t>
+          <t>0.8346 ± 0.0079</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.8456 ± 0.0086</t>
+          <t>0.8329 ± 0.0087</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.144831030464458</v>
+        <v>0.1661395039121024</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.1336372933895762</v>
+        <v>0.1675140096910983</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.1123980330380888</v>
+        <v>0.1644892844235952</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1538323083845805</v>
+        <v>0.1661395039121024</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -4783,104 +5401,104 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9430830697519561</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="C6" t="n">
-        <v>0.003054622010995107</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9486269064274188</v>
+        <v>0.9425705685761205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002733229331666377</v>
+        <v>0.00466313192865296</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9503557108620792</v>
+        <v>0.9427724657852593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.004797011192999022</v>
+        <v>0.004363449095413103</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9469326533673316</v>
+        <v>0.9425420342933244</v>
       </c>
       <c r="I6" t="n">
-        <v>0.004340358980694475</v>
+        <v>0.004713462253088096</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.9431 ± 0.0031</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.9486 ± 0.0027</t>
+          <t>0.9426 ± 0.0047</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.9504 ± 0.0048</t>
+          <t>0.9428 ± 0.0044</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.9469 ± 0.0043</t>
+          <t>0.9425 ± 0.0047</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.7802896620609289</v>
+        <v>0.7628683202929916</v>
       </c>
       <c r="O6" t="n">
-        <v>0.02365755075624813</v>
+        <v>0.02162214626961341</v>
       </c>
       <c r="P6" t="n">
-        <v>0.8034912472240883</v>
+        <v>0.7625153419223542</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02117157621373452</v>
+        <v>0.02252279067347974</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7978041374525189</v>
+        <v>0.7640201225447635</v>
       </c>
       <c r="S6" t="n">
-        <v>0.022863200634055</v>
+        <v>0.02290228574001787</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8095845207739613</v>
+        <v>0.7628683202929916</v>
       </c>
       <c r="U6" t="n">
-        <v>0.02531687241731768</v>
+        <v>0.02162214626961341</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.7803 ± 0.0237</t>
+          <t>0.7629 ± 0.0216</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.8035 ± 0.0212</t>
+          <t>0.7625 ± 0.0225</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.7978 ± 0.0229</t>
+          <t>0.7640 ± 0.0229</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.8096 ± 0.0253</t>
+          <t>0.7629 ± 0.0216</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.1627934076910272</v>
+        <v>0.1796737140003328</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.1451356592033305</v>
+        <v>0.1800552266537664</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.1525515734095603</v>
+        <v>0.1787523432404958</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.1373481325933703</v>
+        <v>0.1796737140003328</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -4895,104 +5513,104 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8177376394206759</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009463270545125387</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8351441635674031</v>
+        <v>0.8247088934359363</v>
       </c>
       <c r="E7" t="n">
-        <v>0.009911515687219402</v>
+        <v>0.003892267554784565</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8380774142407716</v>
+        <v>0.8247249436711384</v>
       </c>
       <c r="G7" t="n">
-        <v>0.007023800154772467</v>
+        <v>0.003908421972607685</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8324883755812209</v>
+        <v>0.8247294822706841</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01907263019534354</v>
+        <v>0.003881194856963221</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8177 ± 0.0095</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.8351 ± 0.0099</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.8381 ± 0.0070</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.8325 ± 0.0191</t>
+          <t>0.8247 ± 0.0039</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.7879473947061761</v>
+        <v>0.7552688530048278</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01187750298864832</v>
+        <v>0.01228916760864686</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8152343871639589</v>
+        <v>0.7551959459542747</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0126440930466092</v>
+        <v>0.01263995609332125</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7887885942352234</v>
+        <v>0.755744437774852</v>
       </c>
       <c r="S7" t="n">
-        <v>0.006890938677445141</v>
+        <v>0.01316604194496796</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8438878056097195</v>
+        <v>0.7552688530048278</v>
       </c>
       <c r="U7" t="n">
-        <v>0.02446228235832</v>
+        <v>0.01228916760864686</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.7879 ± 0.0119</t>
+          <t>0.7553 ± 0.0123</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8152 ± 0.0126</t>
+          <t>0.7552 ± 0.0126</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.7888 ± 0.0069</t>
+          <t>0.7557 ± 0.0132</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.8439 ± 0.0245</t>
+          <t>0.7553 ± 0.0123</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.02979024471449976</v>
+        <v>0.06946062926585628</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.01990977640344416</v>
+        <v>0.06951294748166159</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.04928882000554824</v>
+        <v>0.06898050589628635</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.01139943002849864</v>
+        <v>0.06946062926585628</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -5003,108 +5621,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6532711836191111</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003432765231763527</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7102051701755642</v>
+        <v>0.6593911279336568</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002525563014958159</v>
+        <v>0.006146935199587473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6622882541511838</v>
+        <v>0.6671002535150103</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003196371629185143</v>
+        <v>0.005616591844606063</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7656067196640167</v>
+        <v>0.6584651240219743</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002835651757146686</v>
+        <v>0.006118953967439291</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.6533 ± 0.0034</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.7102 ± 0.0025</t>
+          <t>0.6594 ± 0.0061</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.6623 ± 0.0032</t>
+          <t>0.6671 ± 0.0056</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.7656 ± 0.0028</t>
+          <t>0.6585 ± 0.0061</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.6629432328949559</v>
+        <v>0.6644248376893623</v>
       </c>
       <c r="O8" t="n">
-        <v>0.00567524574843845</v>
+        <v>0.01420251642324667</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6987984491408717</v>
+        <v>0.6604921508095692</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.005611616993817419</v>
+        <v>0.01922134090421259</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6931200354970773</v>
+        <v>0.6639717503612725</v>
       </c>
       <c r="S8" t="n">
-        <v>0.005281692239706439</v>
+        <v>0.01411242551291257</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7046197690115493</v>
+        <v>0.6644248376893623</v>
       </c>
       <c r="U8" t="n">
-        <v>0.00835231995919257</v>
+        <v>0.01420251642324667</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.6629 ± 0.0057</t>
+          <t>0.6644 ± 0.0142</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.6988 ± 0.0056</t>
+          <t>0.6605 ± 0.0192</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.6931 ± 0.0053</t>
+          <t>0.6640 ± 0.0141</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.7046 ± 0.0084</t>
+          <t>0.6644 ± 0.0142</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>-0.009672049275844863</v>
+        <v>-0.005959713667388011</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.01140672103469242</v>
+        <v>-0.001101022875912405</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0.03083178134589359</v>
+        <v>0.003128503153737805</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.0609869506524674</v>
+        <v>-0.005959713667388011</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -5115,108 +5733,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6530214749458965</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="C9" t="n">
-        <v>0.009110561236368791</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6586554205410092</v>
+        <v>0.6487666462408367</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01000642657450882</v>
+        <v>0.0007010223627725054</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7262195138345482</v>
+        <v>0.653007104192831</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02162521657245883</v>
+        <v>0.0006802190230959388</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6036898155092245</v>
+        <v>0.6550357915764941</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02328275950044984</v>
+        <v>0.0006532850631046708</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.6530 ± 0.0091</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.6587 ± 0.0100</t>
+          <t>0.6488 ± 0.0007</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.7262 ± 0.0216</t>
+          <t>0.6530 ± 0.0007</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.6037 ± 0.0233</t>
+          <t>0.6550 ± 0.0007</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.6569668719826869</v>
+        <v>0.6522723489262526</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0109464844492528</v>
+        <v>0.003209173564452282</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7054501163275078</v>
+        <v>0.6447246870404532</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.005909802092955805</v>
+        <v>0.00393454619998641</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6749553590245572</v>
+        <v>0.6505522631114936</v>
       </c>
       <c r="S9" t="n">
-        <v>0.02014059479190419</v>
+        <v>0.003235900172279906</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7405129743512825</v>
+        <v>0.6522723489262526</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02783700788809631</v>
+        <v>0.003209173564452282</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.6570 ± 0.0109</t>
+          <t>0.6523 ± 0.0032</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.7055 ± 0.0059</t>
+          <t>0.6447 ± 0.0039</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.6750 ± 0.0201</t>
+          <t>0.6506 ± 0.0032</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.7405 ± 0.0278</t>
+          <t>0.6523 ± 0.0032</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.003945397036790421</v>
+        <v>0.002763442650241421</v>
       </c>
       <c r="AA9" t="n">
-        <v>-0.04679469578649853</v>
+        <v>0.004041959200383527</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.05126415480999102</v>
+        <v>0.002454841081337422</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.136823158842058</v>
+        <v>0.002763442650241421</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -5231,104 +5849,104 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.652688530048277</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="C10" t="n">
-        <v>0.003540466283100108</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7111657290688942</v>
+        <v>0.6472491388140823</v>
       </c>
       <c r="E10" t="n">
-        <v>0.002515858645437491</v>
+        <v>0.0008797666050638595</v>
       </c>
       <c r="F10" t="n">
-        <v>0.660338278612806</v>
+        <v>0.6522410581225434</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003326244875037613</v>
+        <v>0.0008659629294319769</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7704814759262038</v>
+        <v>0.6541201931080406</v>
       </c>
       <c r="I10" t="n">
-        <v>0.002684656261806534</v>
+        <v>0.0008269807351539551</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.6527 ± 0.0035</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.7112 ± 0.0025</t>
+          <t>0.6472 ± 0.0009</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.6603 ± 0.0033</t>
+          <t>0.6522 ± 0.0009</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.7705 ± 0.0027</t>
+          <t>0.6541 ± 0.0008</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.6626602297319792</v>
+        <v>0.6489512235724987</v>
       </c>
       <c r="O10" t="n">
-        <v>0.005627384388638883</v>
+        <v>0.003448308891968959</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6988185941478678</v>
+        <v>0.6407123832623596</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.005350444122233014</v>
+        <v>0.004257906132352384</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6925340588965098</v>
+        <v>0.6472549050774413</v>
       </c>
       <c r="S10" t="n">
-        <v>0.005459372229371497</v>
+        <v>0.003508859648006634</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7052647367631618</v>
+        <v>0.6489512235724987</v>
       </c>
       <c r="U10" t="n">
-        <v>0.007750128605416733</v>
+        <v>0.003448308891968959</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.6627 ± 0.0056</t>
+          <t>0.6490 ± 0.0034</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.6988 ± 0.0054</t>
+          <t>0.6407 ± 0.0043</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.6925 ± 0.0055</t>
+          <t>0.6473 ± 0.0035</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.7053 ± 0.0078</t>
+          <t>0.6490 ± 0.0034</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>-0.009971699683702262</v>
+        <v>0.005168969535541912</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.01234713492102635</v>
+        <v>0.006536755551722728</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0.03219578028370373</v>
+        <v>0.004986153045102082</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.06521673916304194</v>
+        <v>0.005168969535541912</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -5343,1394 +5961,108 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6093557516231064</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002206246746399765</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5471586204572338</v>
+        <v>0.5949230921311406</v>
       </c>
       <c r="E11" t="n">
-        <v>0.003948342675541275</v>
+        <v>0.001724225896607475</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7669376693867336</v>
+        <v>0.6638581767391858</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002744162729666706</v>
+        <v>0.002274716056977206</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4253037348132593</v>
+        <v>0.6083069751956052</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004574279456311722</v>
+        <v>0.001551660554614313</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.6094 ± 0.0022</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.5472 ± 0.0039</t>
+          <t>0.5949 ± 0.0017</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.7669 ± 0.0027</t>
+          <t>0.6639 ± 0.0023</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.4253 ± 0.0046</t>
+          <t>0.6083 ± 0.0016</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.5940069918428501</v>
+        <v>0.6096221075412019</v>
       </c>
       <c r="O11" t="n">
-        <v>0.004325593662813265</v>
+        <v>0.005555459405745213</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5258634247519973</v>
+        <v>0.5970035031909664</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.007877054735555529</v>
+        <v>0.008812614470602671</v>
       </c>
       <c r="R11" t="n">
-        <v>0.7471363260614226</v>
+        <v>0.6631691510212023</v>
       </c>
       <c r="S11" t="n">
-        <v>0.007472677631446342</v>
+        <v>0.006165808303471135</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4058047097645117</v>
+        <v>0.6096221075412019</v>
       </c>
       <c r="U11" t="n">
-        <v>0.009362764476637342</v>
+        <v>0.005555459405745213</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.5940 ± 0.0043</t>
+          <t>0.6096 ± 0.0056</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.5259 ± 0.0079</t>
+          <t>0.5970 ± 0.0088</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.7471 ± 0.0075</t>
+          <t>0.6632 ± 0.0062</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.4058 ± 0.0094</t>
+          <t>0.6096 ± 0.0056</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.01534875978025629</v>
+        <v>-0.00131513234559677</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.02129519570523652</v>
+        <v>-0.002080411059825815</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.01980134332531103</v>
+        <v>0.0006890257179834602</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.01949902504874756</v>
+        <v>-0.00131513234559677</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
           <t>ForestDiffusion</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AD11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TRTR</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TRTR</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TRTR</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TRTR</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TRTR</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TRTR</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy Std_TSTR</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>F1 Std_TSTR</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Precision Std_TSTR</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Mean_TSTR</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Recall Std_TSTR</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>Precision (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Recall (Mean±Std)_TSTR</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy_Drop</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>F1_Drop</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Precision_Drop</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Recall_Drop</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Synthetic_Model</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ExtraTrees</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.999983352755119</v>
-      </c>
-      <c r="C2" t="n">
-        <v>3.329448976194804e-05</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.9999849996249907</v>
-      </c>
-      <c r="E2" t="n">
-        <v>3.000075001873271e-05</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0.9999700014999249</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.999700014998055e-05</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.0000 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.0000 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>0.4556517396370901</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.01505916985844268</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.5251324138567903</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.02965203013303199</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.508293849138358</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.01220628429477217</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.5448927553622319</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.05282670278344706</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.4557 ± 0.0151</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5251 ± 0.0297</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5083 ± 0.0122</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5449 ± 0.0528</t>
-        </is>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.5443316131180289</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.4748525857682003</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.491706150861642</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.455077246137693</v>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RandomForest</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.9998917929082738</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.814362988976479e-05</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9999025054365672</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3.436305920243479e-05</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.9999100179950515</v>
-      </c>
-      <c r="G3" t="n">
-        <v>9.947206977344203e-05</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9998950052497374</v>
-      </c>
-      <c r="I3" t="n">
-        <v>6.873519866439068e-05</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.9999 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.9999 ± 0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0.9999 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.9999 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.4495172298984518</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.02139291607747043</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.5120664063038667</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.03596609091386745</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.5027788184560051</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.01709804903862116</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.523638818059097</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.06097158979582164</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.4495 ± 0.0214</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.5121 ± 0.0360</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.5028 ± 0.0171</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.5236 ± 0.0610</t>
-        </is>
-      </c>
-      <c r="Z3" t="n">
-        <v>0.550374563009822</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0.4878360991327005</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0.4971311995390464</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0.4762561871906404</v>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MLP</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.9998002330614282</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0001498252039287662</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9998200033725814</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0001350057549300141</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.999835012740364</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.0001414792911934868</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.9998050097495124</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.0001781062259942747</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.9998 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.9998 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>0.9998 ± 0.0001</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>0.9998 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0.4774346595638422</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.01317277090397607</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.532965592982555</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.02309132836844926</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.5283299879552034</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.01015192567167587</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.5387730613469327</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0.04045400898828645</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0.4774 ± 0.0132</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.5330 ± 0.0231</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0.5283 ± 0.0102</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>0.5388 ± 0.0405</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>0.5223655734975861</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.4668544103900264</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0.4715050247851607</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0.4610319484025797</v>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.9993757283169635</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0001870501502766885</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9994375376797811</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0001685162263673175</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9994300667201221</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.0002203628791389911</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9994450277486123</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.0001649917504124697</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.9994 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.9994 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.9994 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.9994 ± 0.0002</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>0.4854752788413517</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.01105508989160575</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.5406892133463262</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.01837093492391009</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.5355723318112794</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.009172088815241492</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5466776661166942</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.03266208874412134</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0.4855 ± 0.0111</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.5407 ± 0.0184</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0.5356 ± 0.0092</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0.5467 ± 0.0327</t>
-        </is>
-      </c>
-      <c r="Z5" t="n">
-        <v>0.5139004494756119</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0.4587483243334548</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0.4638577349088427</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.4527673616319181</v>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>DecisionTree</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.9430830697519561</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.003054622010995107</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9486269064274188</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.002733229331666377</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.9503557108620792</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.004797011192999022</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.9469326533673316</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.004340358980694475</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.9431 ± 0.0031</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.9486 ± 0.0027</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>0.9504 ± 0.0048</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.9469 ± 0.0043</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>0.4905859830198102</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.03061241057693206</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.537626157168307</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.04062901712061393</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.5409967231367535</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.02728335831242973</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.5367181640917955</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.05949013622880233</v>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>0.4906 ± 0.0306</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.5376 ± 0.0406</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0.5410 ± 0.0273</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>0.5367 ± 0.0595</t>
-        </is>
-      </c>
-      <c r="Z6" t="n">
-        <v>0.4524970867321459</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>0.4110007492591118</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>0.4093589877253256</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.4102144892755361</v>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>GradientBoost</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.8177376394206759</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.009463270545125387</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8351441635674031</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.009911515687219402</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8380774142407716</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.007023800154772467</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.8324883755812209</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.01907263019534354</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.8177 ± 0.0095</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.8351 ± 0.0099</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.8381 ± 0.0070</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.8325 ± 0.0191</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>0.4827201598135508</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.018763379920189</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.5697167428891527</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.03232527873997269</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.5283304352657389</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.01280385704440608</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.6208339583020848</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.06568566855493009</v>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0.4827 ± 0.0188</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.5697 ± 0.0323</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>0.5283 ± 0.0128</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0.6208 ± 0.0657</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>0.3350174796071251</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0.2654274206782503</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.3097469789750328</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.2116544172791361</v>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LogReg</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.6532711836191111</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.003432765231763527</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.7102051701755642</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.002525563014958159</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.6622882541511838</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.003196371629185143</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.7656067196640167</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.002835651757146686</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>0.6533 ± 0.0034</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.7102 ± 0.0025</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.6623 ± 0.0032</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.7656 ± 0.0028</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5085983019810223</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.01367199263763621</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.5999205800676521</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.02213500022359702</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.5469010613505055</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.009478453950554485</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.6659217039148043</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0.04799516502372499</v>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0.5086 ± 0.0137</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.5999 ± 0.0221</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0.5469 ± 0.0095</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>0.6659 ± 0.0480</t>
-        </is>
-      </c>
-      <c r="Z8" t="n">
-        <v>0.1446728816380888</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>0.110284590107912</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>0.1153871928006782</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.0996850157492124</v>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AdaBoost</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.6530214749458965</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.009110561236368791</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6586554205410092</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.01000642657450882</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7262195138345482</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.02162521657245883</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.6036898155092245</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.02328275950044984</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.6530 ± 0.0091</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.6587 ± 0.0100</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.7262 ± 0.0216</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.6037 ± 0.0233</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>0.4825703346096221</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.01330375279247198</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.5632326588237714</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.03500931331399579</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.5292177139210736</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.009308951685638384</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0.6064196790160492</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0.07512839714970289</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0.4826 ± 0.0133</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.5632 ± 0.0350</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0.5292 ± 0.0093</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0.6064 ± 0.0751</t>
-        </is>
-      </c>
-      <c r="Z9" t="n">
-        <v>0.1704511403362744</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0.09542276171723785</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0.1970017999134746</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>-0.002729863506824692</v>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SVM-RBF</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.652688530048277</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.003540466283100108</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.7111657290688942</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.002515858645437491</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.660338278612806</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.003326244875037613</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.7704814759262038</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.002684656261806534</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.6527 ± 0.0035</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.7112 ± 0.0025</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>0.6603 ± 0.0033</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.7705 ± 0.0027</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>0.5084984185117364</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.01407019435272617</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.5991782477315457</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.02241384616919643</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.5469659598092009</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.00985408369532533</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0.6640167991600421</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0.04816324349956423</v>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0.5085 ± 0.0141</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.5992 ± 0.0224</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0.5470 ± 0.0099</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0.6640 ± 0.0482</t>
-        </is>
-      </c>
-      <c r="Z10" t="n">
-        <v>0.1441901115365406</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.1119874813373485</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0.1133723188036051</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.1064646767661617</v>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NaiveBayes</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.6093557516231064</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.002206246746399765</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.5471586204572338</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.003948342675541275</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.7669376693867336</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.002744162729666706</v>
-      </c>
-      <c r="H11" t="n">
-        <v>0.4253037348132593</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.004574279456311722</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.6094 ± 0.0022</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.5472 ± 0.0039</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>0.7669 ± 0.0027</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.4253 ± 0.0046</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>0.5128849675378724</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.0129711738548142</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.6408896636018478</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.02136845704392922</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.5421369235868775</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.007397371420856608</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0.7862906854657268</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0.06096997914441964</v>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0.5129 ± 0.0130</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.6409 ± 0.0214</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>0.5421 ± 0.0074</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>0.7863 ± 0.0610</t>
-        </is>
-      </c>
-      <c r="Z11" t="n">
-        <v>0.09647078408523402</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>-0.093731043144614</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0.2248007457998561</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-0.3609869506524675</v>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>TabDDPM</t>
         </is>
       </c>
     </row>
